--- a/doc/customer.xlsx
+++ b/doc/customer.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7000"/>
+    <workbookView windowWidth="20994" windowHeight="13141"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,10 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="135">
-  <si>
-    <t>表头</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="132">
   <si>
     <t>分配方式</t>
   </si>
@@ -167,9 +164,6 @@
     <t>聊天记录</t>
   </si>
   <si>
-    <t>示例</t>
-  </si>
-  <si>
     <t>手动</t>
   </si>
   <si>
@@ -399,9 +393,6 @@
   </si>
   <si>
     <t>1c133a95a54c41a1b2d57990c987f0e2</t>
-  </si>
-  <si>
-    <t>需求</t>
   </si>
   <si>
     <t>手动
@@ -621,18 +612,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -974,7 +959,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -998,16 +983,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1016,106 +1001,97 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1645,1344 +1621,1322 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AT11"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <dimension ref="A1:AS11"/>
+  <sheetFormatPr defaultColWidth="8.72477064220183" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="70" spans="1:46">
+    <row r="1" s="1" customFormat="1" ht="87.75" spans="1:45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AI1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AL1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AM1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AN1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AO1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AP1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AR1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AS1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="3" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:45">
+      <c r="A2" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:46">
-      <c r="A2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="F2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>52</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AO2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AR2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:45">
+      <c r="A3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="P3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:45">
+      <c r="A4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="P4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="AB4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AO4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AP4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS4" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:45">
+      <c r="A5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="U2" s="1" t="s">
+      <c r="R5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AO5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AP5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AR5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS5" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:45">
+      <c r="A6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="V2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="X2" s="1" t="s">
+      <c r="AE6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK6" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AO6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AP6" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS6" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:45">
+      <c r="A7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AO7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AP7" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AR7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS7" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:45">
+      <c r="A8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK8" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AL8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AO8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AP8" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AR8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS8" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:45">
+      <c r="A9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="V9" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="W9" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z9" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AE9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF9" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AG9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK9" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AL9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AO9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AP9" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS9" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:45">
+      <c r="A10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="O10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AD2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AB10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF10" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AF2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AL2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AM2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AN2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AO2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AP2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AQ2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AR2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AS2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT2" s="1" t="s">
-        <v>52</v>
+      <c r="AH10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK10" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AL10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AO10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AP10" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AR10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS10" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:46">
-      <c r="A3" s="4"/>
-      <c r="B3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE3" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG3" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH3" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AL3" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AN3" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AO3" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AP3" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AQ3" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AS3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT3" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:46">
-      <c r="A4" s="4"/>
-      <c r="B4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE4" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AL4" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AM4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AN4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AO4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AP4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AQ4" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AS4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT4" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:46">
-      <c r="A5" s="4"/>
-      <c r="B5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="V5" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA5" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE5" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AF5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG5" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH5" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AL5" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AM5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AN5" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AO5" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AP5" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AQ5" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT5" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:46">
-      <c r="A6" s="4"/>
-      <c r="B6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA6" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE6" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH6" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AL6" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AM6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AN6" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AO6" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AP6" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AQ6" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AS6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT6" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:46">
-      <c r="A7" s="4"/>
-      <c r="B7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE7" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AF7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG7" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AL7" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AM7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AN7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AO7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AP7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AQ7" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="AS7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT7" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:46">
-      <c r="A8" s="4"/>
-      <c r="B8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE8" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AF8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG8" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH8" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AL8" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="AM8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AN8" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AO8" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AP8" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AQ8" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="AS8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT8" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:46">
-      <c r="A9" s="4"/>
-      <c r="B9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="V9" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="W9" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y9" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA9" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AF9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG9" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH9" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AL9" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AM9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AN9" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AO9" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AP9" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AQ9" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AS9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT9" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:46">
-      <c r="A10" s="4"/>
-      <c r="B10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="V10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA10" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AB10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE10" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG10" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AL10" s="1" t="s">
+    <row r="11" ht="101" customHeight="1" spans="1:45">
+      <c r="A11" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="AM10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AN10" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AO10" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AP10" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AQ10" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="AS10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT10" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" ht="101" customHeight="1" spans="1:46">
-      <c r="A11" s="5" t="s">
+      <c r="D11" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="G11" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="I11" t="s">
         <v>126</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="J11" t="s">
+        <v>126</v>
+      </c>
+      <c r="N11" t="s">
+        <v>126</v>
+      </c>
+      <c r="O11" t="s">
+        <v>126</v>
+      </c>
+      <c r="P11" t="s">
         <v>127</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="Q11" t="s">
         <v>128</v>
       </c>
-      <c r="J11" t="s">
+      <c r="T11" t="s">
+        <v>127</v>
+      </c>
+      <c r="U11" t="s">
+        <v>127</v>
+      </c>
+      <c r="V11" t="s">
         <v>129</v>
       </c>
-      <c r="K11" t="s">
+      <c r="W11" t="s">
         <v>129</v>
       </c>
-      <c r="L11"/>
-      <c r="M11"/>
-      <c r="O11" t="s">
-        <v>129</v>
-      </c>
-      <c r="P11" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q11" t="s">
+      <c r="Z11" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="R11" t="s">
+      <c r="AA11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AG11" t="s">
         <v>131</v>
       </c>
-      <c r="U11" t="s">
-        <v>130</v>
-      </c>
-      <c r="V11" t="s">
-        <v>130</v>
-      </c>
-      <c r="W11" t="s">
-        <v>132</v>
-      </c>
-      <c r="X11" t="s">
-        <v>132</v>
-      </c>
-      <c r="AA11" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>129</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>134</v>
+      <c r="AM11" t="s">
+        <v>131</v>
       </c>
       <c r="AN11" t="s">
-        <v>134</v>
-      </c>
-      <c r="AO11" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR11" t="s">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:A10"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
